--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="633" activeTab="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="633" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -2071,7 +2071,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G4">
         <v>5</v>

--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -851,7 +851,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2140,7 +2140,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="18">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -2160,7 +2160,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="18">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -2180,7 +2180,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="18">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -2200,7 +2200,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="18">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -2220,7 +2220,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="18">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>

--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="633" activeTab="3"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="633" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -851,7 +851,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1608,7 +1608,7 @@
         <v>63</v>
       </c>
       <c r="E8" s="2">
-        <v>250</v>
+        <v>850</v>
       </c>
       <c r="F8" s="2">
         <v>10</v>
@@ -1759,7 +1759,7 @@
         <v>63</v>
       </c>
       <c r="E16" s="2">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="F16" s="2">
         <v>10</v>
@@ -1905,7 +1905,7 @@
         <v>63</v>
       </c>
       <c r="E25" s="2">
-        <v>25000</v>
+        <v>45000</v>
       </c>
       <c r="F25" s="2">
         <v>10</v>

--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="633" activeTab="2"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="633" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -1130,7 +1130,7 @@
         <v>1001</v>
       </c>
       <c r="M4">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
@@ -1175,7 +1175,7 @@
         <v>1002</v>
       </c>
       <c r="M5">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
@@ -1220,7 +1220,7 @@
         <v>1003</v>
       </c>
       <c r="M6">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
@@ -1265,7 +1265,7 @@
         <v>2001</v>
       </c>
       <c r="M7">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
@@ -1309,7 +1309,7 @@
         <v>3000</v>
       </c>
       <c r="M8">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>

--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -2373,44 +2373,160 @@
     </row>
     <row r="15">
       <c r="A15" s="8" t="n"/>
-      <c r="F15" s="18" t="n"/>
+      <c r="B15" t="n">
+        <v>12</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>10001</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
       <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n"/>
+      <c r="B16" t="n">
+        <v>13</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4001</v>
+      </c>
+      <c r="D16" t="n">
+        <v>10002</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
       <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
+      <c r="B17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>4001</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>10003</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
+      <c r="B18" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>4002</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>10001</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>12</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
       <c r="H18" s="2" t="n"/>
       <c r="I18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n"/>
-      <c r="B19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
+      <c r="B19" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4002</v>
+      </c>
+      <c r="D19" t="n">
+        <v>10002</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
       <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n"/>
-      <c r="B20" s="6" t="n"/>
+      <c r="B20" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4002</v>
+      </c>
+      <c r="D20" t="n">
+        <v>10003</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n"/>
+      <c r="B21" t="n">
+        <v>18</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4002</v>
+      </c>
+      <c r="D21" t="n">
+        <v>20001</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="n"/>
     </row>

--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="101">
   <si>
     <t>!Enum</t>
   </si>
@@ -286,26 +286,60 @@
   </si>
   <si>
     <t>Skill_Monster_OrcGeneral_Active_01</t>
+  </si>
+  <si>
+    <t>Skill_Monster_OrcGeneral_Active_01</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Monster_CastAttack_01</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>유적 코어</t>
+  </si>
+  <si>
+    <t>유적을 지키는 방어 시스템의 핵</t>
+  </si>
+  <si>
+    <t>유적 방어장치</t>
+  </si>
+  <si>
+    <t>유적에 설치된 고정 포대</t>
+  </si>
+  <si>
+    <t>유적 가디언</t>
+  </si>
+  <si>
+    <t>코어가 불러내는 유적의 수호자</t>
+  </si>
+  <si>
+    <t>Skill_Monster_Boss_MeleeAttack_01</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Monster_Boss_MeleeAttack_01</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Monster_Boss_MeleeAttack_01</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Monster_Boss_MeleeAttack_01</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -506,15 +540,15 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -528,30 +562,24 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -564,19 +592,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -959,7 +987,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -970,7 +998,7 @@
   <dimension ref="A1:T18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" style="23" customWidth="1"/>
+    <col min="1" max="1" width="9" style="21" customWidth="1"/>
     <col min="2" max="2" width="8.5" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.625" style="2" bestFit="1" customWidth="1"/>
@@ -988,53 +1016,53 @@
     <col min="26" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:20" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A2" s="8"/>
-      <c r="B2" s="6" t="s">
+      <c r="A2" s="7"/>
+      <c r="B2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="16" t="s">
+      <c r="E2" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="14" t="s">
         <v>23</v>
       </c>
       <c r="G2" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="16" t="s">
         <v>26</v>
       </c>
       <c r="K2" t="s">
         <v>27</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="L2" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="M2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="N2" s="16" t="s">
+      <c r="N2" s="14" t="s">
         <v>30</v>
       </c>
       <c r="O2" s="2" t="s">
@@ -1046,38 +1074,38 @@
       <c r="T2" s="2"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="18" t="s">
+      <c r="A3" s="7"/>
+      <c r="B3" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="13" t="s">
         <v>33</v>
       </c>
       <c r="G3" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="J3" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="K3" s="18" t="s">
+      <c r="K3" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="L3" s="16" t="s">
+      <c r="L3" s="14" t="s">
         <v>32</v>
       </c>
       <c r="M3" t="s">
@@ -1096,7 +1124,7 @@
       <c r="T3" s="2"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
+      <c r="A4" s="7"/>
       <c r="B4">
         <v>10001</v>
       </c>
@@ -1121,13 +1149,13 @@
       <c r="I4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="18">
+      <c r="J4" s="16">
         <v>5</v>
       </c>
-      <c r="K4" s="18">
+      <c r="K4" s="16">
         <v>10</v>
       </c>
-      <c r="L4" s="19">
+      <c r="L4" s="17">
         <v>1001</v>
       </c>
       <c r="M4">
@@ -1143,7 +1171,7 @@
       <c r="T4" s="2"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
+      <c r="A5" s="7"/>
       <c r="B5">
         <v>10002</v>
       </c>
@@ -1171,10 +1199,10 @@
       <c r="J5">
         <v>5</v>
       </c>
-      <c r="K5" s="18">
+      <c r="K5" s="16">
         <v>10</v>
       </c>
-      <c r="L5" s="19">
+      <c r="L5" s="17">
         <v>1002</v>
       </c>
       <c r="M5">
@@ -1190,7 +1218,7 @@
       <c r="T5" s="2"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
+      <c r="A6" s="7"/>
       <c r="B6">
         <v>10003</v>
       </c>
@@ -1218,10 +1246,10 @@
       <c r="J6">
         <v>5</v>
       </c>
-      <c r="K6" s="18">
+      <c r="K6" s="16">
         <v>10</v>
       </c>
-      <c r="L6" s="19">
+      <c r="L6" s="17">
         <v>1003</v>
       </c>
       <c r="M6">
@@ -1237,7 +1265,7 @@
       <c r="T6" s="2"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
+      <c r="A7" s="7"/>
       <c r="B7">
         <v>20001</v>
       </c>
@@ -1268,7 +1296,7 @@
       <c r="K7">
         <v>10</v>
       </c>
-      <c r="L7" s="19">
+      <c r="L7" s="17">
         <v>2001</v>
       </c>
       <c r="M7">
@@ -1282,7 +1310,7 @@
       <c r="T7" s="2"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>30001</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -1306,13 +1334,13 @@
       <c r="I8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="18">
+      <c r="J8" s="16">
         <v>5</v>
       </c>
       <c r="K8">
         <v>8</v>
       </c>
-      <c r="L8" s="19">
+      <c r="L8" s="17">
         <v>3000</v>
       </c>
       <c r="M8">
@@ -1326,11 +1354,42 @@
       <c r="T8" s="2"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B9" s="6"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="18"/>
-      <c r="L9" s="19"/>
+      <c r="B9" s="5">
+        <v>30101</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9">
+        <v>30101</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="16">
+        <v>3</v>
+      </c>
+      <c r="K9">
+        <v>99</v>
+      </c>
+      <c r="L9" s="17">
+        <v>1001</v>
+      </c>
+      <c r="M9">
+        <v>500</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
@@ -1339,8 +1398,42 @@
       <c r="T9" s="2"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="6"/>
+      <c r="B10" s="5">
+        <v>20101</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10">
+        <v>20101</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="16">
+        <v>7</v>
+      </c>
+      <c r="K10">
+        <v>99</v>
+      </c>
+      <c r="L10" s="17">
+        <v>1003</v>
+      </c>
+      <c r="M10">
+        <v>150</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
@@ -1348,11 +1441,43 @@
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
     </row>
-    <row r="11" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="6"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="11"/>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B11" s="5">
+        <v>10101</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11">
+        <v>10101</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="16">
+        <v>8</v>
+      </c>
+      <c r="K11">
+        <v>15</v>
+      </c>
+      <c r="L11" s="17">
+        <v>1001</v>
+      </c>
+      <c r="M11">
+        <v>75</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
@@ -1361,10 +1486,10 @@
       <c r="T11" s="2"/>
     </row>
     <row r="12" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C12" s="18"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="11"/>
-      <c r="L12" s="19"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="10"/>
+      <c r="L12" s="17"/>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
@@ -1373,8 +1498,8 @@
       <c r="T12" s="2"/>
     </row>
     <row r="13" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E13" s="11"/>
-      <c r="L13" s="19"/>
+      <c r="E13" s="10"/>
+      <c r="L13" s="17"/>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
@@ -1383,10 +1508,10 @@
       <c r="T13" s="2"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="C14" s="18"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="18"/>
-      <c r="L14" s="19"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="16"/>
+      <c r="L14" s="17"/>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
@@ -1395,9 +1520,9 @@
       <c r="T14" s="2"/>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
@@ -1406,7 +1531,7 @@
       <c r="T15" s="2"/>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="E16" s="13"/>
+      <c r="E16" s="12"/>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
@@ -1415,7 +1540,7 @@
       <c r="T16" s="2"/>
     </row>
     <row r="17" spans="5:20" x14ac:dyDescent="0.3">
-      <c r="E17" s="13"/>
+      <c r="E17" s="12"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -1432,7 +1557,7 @@
       <c r="T17" s="2"/>
     </row>
     <row r="18" spans="5:20" x14ac:dyDescent="0.3">
-      <c r="E18" s="13"/>
+      <c r="E18" s="12"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -1449,7 +1574,7 @@
       <c r="T18" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -1457,10 +1582,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" style="23" customWidth="1"/>
+    <col min="1" max="1" width="9" style="21" customWidth="1"/>
     <col min="2" max="2" width="11.875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.75" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="31.25" style="2" bestFit="1" customWidth="1"/>
@@ -1472,55 +1597,55 @@
     <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="8"/>
-      <c r="B2" s="6" t="s">
+      <c r="A2" s="7"/>
+      <c r="B2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="16" t="s">
         <v>55</v>
       </c>
       <c r="E2" t="s">
         <v>56</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="16"/>
+      <c r="G2" s="14"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="18" t="s">
+      <c r="A3" s="7"/>
+      <c r="B3" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="16" t="s">
         <v>37</v>
       </c>
       <c r="H3" s="2"/>
@@ -1528,7 +1653,7 @@
       <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
+      <c r="A4" s="7"/>
       <c r="B4">
         <v>1</v>
       </c>
@@ -1549,7 +1674,7 @@
       <c r="J4" s="2"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
+      <c r="A5" s="7"/>
       <c r="B5">
         <v>2</v>
       </c>
@@ -1567,7 +1692,7 @@
       <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
+      <c r="A6" s="7"/>
       <c r="B6">
         <v>3</v>
       </c>
@@ -1586,7 +1711,7 @@
       <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
+      <c r="A7" s="7"/>
       <c r="B7">
         <v>4</v>
       </c>
@@ -1647,7 +1772,7 @@
       <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
+      <c r="A10" s="7"/>
       <c r="B10">
         <v>7</v>
       </c>
@@ -1977,8 +2102,365 @@
         <v>300</v>
       </c>
     </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B30">
+        <v>27</v>
+      </c>
+      <c r="C30">
+        <v>30101</v>
+      </c>
+      <c r="D30" t="s">
+        <v>59</v>
+      </c>
+      <c r="E30">
+        <v>10</v>
+      </c>
+      <c r="F30" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B31">
+        <v>28</v>
+      </c>
+      <c r="C31">
+        <v>30101</v>
+      </c>
+      <c r="D31" t="s">
+        <v>60</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B32">
+        <v>29</v>
+      </c>
+      <c r="C32">
+        <v>30101</v>
+      </c>
+      <c r="D32" t="s">
+        <v>61</v>
+      </c>
+      <c r="E32">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B33">
+        <v>30</v>
+      </c>
+      <c r="C33">
+        <v>30101</v>
+      </c>
+      <c r="D33" t="s">
+        <v>62</v>
+      </c>
+      <c r="E33">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B34">
+        <v>31</v>
+      </c>
+      <c r="C34">
+        <v>30101</v>
+      </c>
+      <c r="D34" t="s">
+        <v>63</v>
+      </c>
+      <c r="E34">
+        <v>30000</v>
+      </c>
+      <c r="F34" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B35">
+        <v>32</v>
+      </c>
+      <c r="C35">
+        <v>30101</v>
+      </c>
+      <c r="D35" t="s">
+        <v>65</v>
+      </c>
+      <c r="E35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B36">
+        <v>33</v>
+      </c>
+      <c r="C36">
+        <v>30101</v>
+      </c>
+      <c r="D36" t="s">
+        <v>66</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B37">
+        <v>34</v>
+      </c>
+      <c r="C37">
+        <v>30101</v>
+      </c>
+      <c r="D37" t="s">
+        <v>67</v>
+      </c>
+      <c r="E37">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B38">
+        <v>35</v>
+      </c>
+      <c r="C38">
+        <v>20101</v>
+      </c>
+      <c r="D38" t="s">
+        <v>59</v>
+      </c>
+      <c r="E38">
+        <v>10</v>
+      </c>
+      <c r="F38" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B39">
+        <v>36</v>
+      </c>
+      <c r="C39">
+        <v>20101</v>
+      </c>
+      <c r="D39" t="s">
+        <v>60</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B40">
+        <v>37</v>
+      </c>
+      <c r="C40">
+        <v>20101</v>
+      </c>
+      <c r="D40" t="s">
+        <v>61</v>
+      </c>
+      <c r="E40">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B41">
+        <v>38</v>
+      </c>
+      <c r="C41">
+        <v>20101</v>
+      </c>
+      <c r="D41" t="s">
+        <v>62</v>
+      </c>
+      <c r="E41">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B42">
+        <v>39</v>
+      </c>
+      <c r="C42">
+        <v>20101</v>
+      </c>
+      <c r="D42" t="s">
+        <v>63</v>
+      </c>
+      <c r="E42">
+        <v>3000</v>
+      </c>
+      <c r="F42" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B43">
+        <v>40</v>
+      </c>
+      <c r="C43">
+        <v>20101</v>
+      </c>
+      <c r="D43" t="s">
+        <v>65</v>
+      </c>
+      <c r="E43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B44">
+        <v>41</v>
+      </c>
+      <c r="C44">
+        <v>20101</v>
+      </c>
+      <c r="D44" t="s">
+        <v>66</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B45">
+        <v>42</v>
+      </c>
+      <c r="C45">
+        <v>20101</v>
+      </c>
+      <c r="D45" t="s">
+        <v>67</v>
+      </c>
+      <c r="E45">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B46">
+        <v>43</v>
+      </c>
+      <c r="C46">
+        <v>10101</v>
+      </c>
+      <c r="D46" t="s">
+        <v>59</v>
+      </c>
+      <c r="E46">
+        <v>10</v>
+      </c>
+      <c r="F46" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B47">
+        <v>44</v>
+      </c>
+      <c r="C47">
+        <v>10101</v>
+      </c>
+      <c r="D47" t="s">
+        <v>60</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B48">
+        <v>45</v>
+      </c>
+      <c r="C48">
+        <v>10101</v>
+      </c>
+      <c r="D48" t="s">
+        <v>61</v>
+      </c>
+      <c r="E48">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B49">
+        <v>46</v>
+      </c>
+      <c r="C49">
+        <v>10101</v>
+      </c>
+      <c r="D49" t="s">
+        <v>62</v>
+      </c>
+      <c r="E49">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B50">
+        <v>47</v>
+      </c>
+      <c r="C50">
+        <v>10101</v>
+      </c>
+      <c r="D50" t="s">
+        <v>63</v>
+      </c>
+      <c r="E50">
+        <v>1500</v>
+      </c>
+      <c r="F50" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B51">
+        <v>48</v>
+      </c>
+      <c r="C51">
+        <v>10101</v>
+      </c>
+      <c r="D51" t="s">
+        <v>64</v>
+      </c>
+      <c r="E51">
+        <v>5</v>
+      </c>
+      <c r="F51" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B52">
+        <v>49</v>
+      </c>
+      <c r="C52">
+        <v>10101</v>
+      </c>
+      <c r="D52" t="s">
+        <v>65</v>
+      </c>
+      <c r="E52">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B53">
+        <v>50</v>
+      </c>
+      <c r="C53">
+        <v>10101</v>
+      </c>
+      <c r="D53" t="s">
+        <v>66</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -1986,10 +2468,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" style="23" customWidth="1"/>
+    <col min="1" max="1" width="9" style="21" customWidth="1"/>
     <col min="2" max="2" width="12.5" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.75" style="2" customWidth="1"/>
     <col min="4" max="4" width="10.375" style="2" bestFit="1" customWidth="1"/>
@@ -2002,23 +2484,23 @@
     <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:9" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="8"/>
-      <c r="B2" s="6" t="s">
+      <c r="A2" s="7"/>
+      <c r="B2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D2" t="s">
@@ -2039,32 +2521,32 @@
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="18" t="s">
+      <c r="A3" s="7"/>
+      <c r="B3" s="16" t="s">
         <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="16" t="s">
         <v>32</v>
       </c>
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
+      <c r="A4" s="7"/>
       <c r="B4">
         <v>1</v>
       </c>
@@ -2074,10 +2556,10 @@
       <c r="D4">
         <v>10001</v>
       </c>
-      <c r="E4" s="18">
-        <v>1</v>
-      </c>
-      <c r="F4" s="18">
+      <c r="E4" s="16">
+        <v>1</v>
+      </c>
+      <c r="F4" s="16">
         <v>5</v>
       </c>
       <c r="G4">
@@ -2087,7 +2569,7 @@
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
+      <c r="A5" s="7"/>
       <c r="B5">
         <v>2</v>
       </c>
@@ -2097,10 +2579,10 @@
       <c r="D5">
         <v>10002</v>
       </c>
-      <c r="E5" s="18">
-        <v>1</v>
-      </c>
-      <c r="F5" s="18">
+      <c r="E5" s="16">
+        <v>1</v>
+      </c>
+      <c r="F5" s="16">
         <v>2</v>
       </c>
       <c r="G5">
@@ -2110,7 +2592,7 @@
       <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
+      <c r="A6" s="7"/>
       <c r="B6">
         <v>3</v>
       </c>
@@ -2120,10 +2602,10 @@
       <c r="D6">
         <v>10003</v>
       </c>
-      <c r="E6" s="18">
-        <v>1</v>
-      </c>
-      <c r="F6" s="18">
+      <c r="E6" s="16">
+        <v>1</v>
+      </c>
+      <c r="F6" s="16">
         <v>1</v>
       </c>
       <c r="G6">
@@ -2133,7 +2615,7 @@
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
+      <c r="A7" s="7"/>
       <c r="B7">
         <v>4</v>
       </c>
@@ -2143,17 +2625,17 @@
       <c r="D7">
         <v>10001</v>
       </c>
-      <c r="E7" s="18">
-        <v>1</v>
-      </c>
-      <c r="F7" s="18">
+      <c r="E7" s="16">
+        <v>1</v>
+      </c>
+      <c r="F7" s="16">
         <v>100</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
+      <c r="A8" s="7"/>
       <c r="B8">
         <v>5</v>
       </c>
@@ -2163,17 +2645,17 @@
       <c r="D8">
         <v>10001</v>
       </c>
-      <c r="E8" s="18">
-        <v>1</v>
-      </c>
-      <c r="F8" s="18">
+      <c r="E8" s="16">
+        <v>1</v>
+      </c>
+      <c r="F8" s="16">
         <v>80</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
+      <c r="A9" s="7"/>
       <c r="B9">
         <v>6</v>
       </c>
@@ -2183,17 +2665,17 @@
       <c r="D9">
         <v>10002</v>
       </c>
-      <c r="E9" s="18">
-        <v>1</v>
-      </c>
-      <c r="F9" s="18">
+      <c r="E9" s="16">
+        <v>1</v>
+      </c>
+      <c r="F9" s="16">
         <v>45</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
+      <c r="A10" s="7"/>
       <c r="B10">
         <v>7</v>
       </c>
@@ -2203,17 +2685,17 @@
       <c r="D10">
         <v>10001</v>
       </c>
-      <c r="E10" s="18">
-        <v>1</v>
-      </c>
-      <c r="F10" s="18">
+      <c r="E10" s="16">
+        <v>1</v>
+      </c>
+      <c r="F10" s="16">
         <v>100</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
+      <c r="A11" s="7"/>
       <c r="B11">
         <v>8</v>
       </c>
@@ -2223,17 +2705,17 @@
       <c r="D11">
         <v>10002</v>
       </c>
-      <c r="E11" s="18">
-        <v>1</v>
-      </c>
-      <c r="F11" s="18">
+      <c r="E11" s="16">
+        <v>1</v>
+      </c>
+      <c r="F11" s="16">
         <v>50</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
+      <c r="A12" s="7"/>
       <c r="B12">
         <v>9</v>
       </c>
@@ -2243,17 +2725,17 @@
       <c r="D12">
         <v>10003</v>
       </c>
-      <c r="E12" s="18">
-        <v>1</v>
-      </c>
-      <c r="F12" s="18">
+      <c r="E12" s="16">
+        <v>1</v>
+      </c>
+      <c r="F12" s="16">
         <v>10</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
+      <c r="A13" s="7"/>
       <c r="B13">
         <v>10</v>
       </c>
@@ -2263,10 +2745,10 @@
       <c r="D13">
         <v>20001</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="16">
         <v>5</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="16">
         <v>1</v>
       </c>
       <c r="G13">
@@ -2276,7 +2758,7 @@
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
+      <c r="A14" s="7"/>
       <c r="B14">
         <v>11</v>
       </c>
@@ -2289,7 +2771,7 @@
       <c r="E14" s="2">
         <v>10</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="16">
         <v>1</v>
       </c>
       <c r="G14">
@@ -2299,7 +2781,7 @@
       <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
+      <c r="A15" s="7"/>
       <c r="B15">
         <v>12</v>
       </c>
@@ -2312,7 +2794,7 @@
       <c r="E15">
         <v>1</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="16">
         <v>12</v>
       </c>
       <c r="G15">
@@ -2322,7 +2804,7 @@
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
+      <c r="A16" s="7"/>
       <c r="B16">
         <v>13</v>
       </c>
@@ -2348,13 +2830,13 @@
       <c r="B17">
         <v>14</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="5">
         <v>4001</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="5">
         <v>10003</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="5">
         <v>1</v>
       </c>
       <c r="F17">
@@ -2370,13 +2852,13 @@
       <c r="B18">
         <v>15</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="5">
         <v>4002</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="5">
         <v>10001</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="5">
         <v>1</v>
       </c>
       <c r="F18">
@@ -2389,8 +2871,8 @@
       <c r="I18" s="2"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="6">
+      <c r="A19" s="7"/>
+      <c r="B19" s="5">
         <v>16</v>
       </c>
       <c r="C19">
@@ -2399,7 +2881,7 @@
       <c r="D19">
         <v>10002</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="5">
         <v>1</v>
       </c>
       <c r="F19">
@@ -2412,8 +2894,8 @@
       <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="6">
+      <c r="A20" s="7"/>
+      <c r="B20" s="5">
         <v>17</v>
       </c>
       <c r="C20">
@@ -2435,7 +2917,7 @@
       <c r="I20" s="2"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
+      <c r="A21" s="7"/>
       <c r="B21">
         <v>18</v>
       </c>
@@ -2458,7 +2940,7 @@
       <c r="I21" s="2"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
+      <c r="A22" s="7"/>
       <c r="B22" s="2">
         <v>19</v>
       </c>
@@ -2481,7 +2963,7 @@
       <c r="I22" s="2"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
+      <c r="A23" s="7"/>
       <c r="B23" s="2">
         <v>20</v>
       </c>
@@ -2504,7 +2986,7 @@
       <c r="I23" s="2"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
+      <c r="A24" s="7"/>
       <c r="B24" s="2">
         <v>21</v>
       </c>
@@ -2527,7 +3009,7 @@
       <c r="I24" s="2"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
+      <c r="A25" s="7"/>
       <c r="B25" s="2">
         <v>22</v>
       </c>
@@ -2550,7 +3032,7 @@
       <c r="I25" s="2"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
+      <c r="A26" s="7"/>
       <c r="B26" s="2">
         <v>23</v>
       </c>
@@ -2573,7 +3055,7 @@
       <c r="I26" s="2"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
+      <c r="A27" s="7"/>
       <c r="B27" s="2">
         <v>24</v>
       </c>
@@ -2596,7 +3078,7 @@
       <c r="I27" s="2"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
+      <c r="A28" s="7"/>
       <c r="B28" s="2">
         <v>25</v>
       </c>
@@ -3116,8 +3598,68 @@
         <v>0</v>
       </c>
     </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B54" s="2">
+        <v>51</v>
+      </c>
+      <c r="C54" s="2">
+        <v>6001</v>
+      </c>
+      <c r="D54" s="2">
+        <v>30101</v>
+      </c>
+      <c r="E54" s="2">
+        <v>1</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B55" s="2">
+        <v>52</v>
+      </c>
+      <c r="C55" s="2">
+        <v>6002</v>
+      </c>
+      <c r="D55" s="2">
+        <v>20101</v>
+      </c>
+      <c r="E55" s="2">
+        <v>1</v>
+      </c>
+      <c r="F55">
+        <v>4</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B56" s="2">
+        <v>53</v>
+      </c>
+      <c r="C56" s="2">
+        <v>6003</v>
+      </c>
+      <c r="D56" s="2">
+        <v>10101</v>
+      </c>
+      <c r="E56" s="2">
+        <v>1</v>
+      </c>
+      <c r="F56">
+        <v>4</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3127,7 +3669,7 @@
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.625" style="23" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.625" style="21" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
@@ -3138,11 +3680,11 @@
     <col min="9" max="9" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="19" t="s">
         <v>73</v>
       </c>
     </row>
@@ -3280,7 +3822,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -3288,21 +3830,21 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" style="23" customWidth="1"/>
+    <col min="1" max="1" width="9" style="21" customWidth="1"/>
     <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="34.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="19" t="s">
         <v>82</v>
       </c>
     </row>
@@ -3415,7 +3957,7 @@
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -3471,7 +4013,7 @@
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -3485,7 +4027,7 @@
         <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -3493,13 +4035,13 @@
         <v>12</v>
       </c>
       <c r="C15">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -3507,13 +4049,13 @@
         <v>13</v>
       </c>
       <c r="C16">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
@@ -3521,13 +4063,13 @@
         <v>14</v>
       </c>
       <c r="C17">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E17" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
@@ -3535,13 +4077,13 @@
         <v>15</v>
       </c>
       <c r="C18">
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E18" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
@@ -3549,13 +4091,13 @@
         <v>16</v>
       </c>
       <c r="C19">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
@@ -3563,17 +4105,199 @@
         <v>17</v>
       </c>
       <c r="C20">
+        <v>3002</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <v>18</v>
+      </c>
+      <c r="C21">
+        <v>3002</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B22">
+        <v>19</v>
+      </c>
+      <c r="C22">
+        <v>3002</v>
+      </c>
+      <c r="D22">
+        <v>4</v>
+      </c>
+      <c r="E22" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <v>20</v>
+      </c>
+      <c r="C23">
+        <v>3002</v>
+      </c>
+      <c r="D23">
+        <v>5</v>
+      </c>
+      <c r="E23" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B24">
+        <v>21</v>
+      </c>
+      <c r="C24">
+        <v>3002</v>
+      </c>
+      <c r="D24">
+        <v>6</v>
+      </c>
+      <c r="E24" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B25">
+        <v>22</v>
+      </c>
+      <c r="C25">
+        <v>3002</v>
+      </c>
+      <c r="D25">
+        <v>7</v>
+      </c>
+      <c r="E25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B26">
+        <v>23</v>
+      </c>
+      <c r="C26">
         <v>3003</v>
       </c>
-      <c r="D20">
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B27">
+        <v>24</v>
+      </c>
+      <c r="C27">
+        <v>3003</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B28">
+        <v>25</v>
+      </c>
+      <c r="C28">
+        <v>3003</v>
+      </c>
+      <c r="D28">
         <v>3</v>
       </c>
-      <c r="E20" t="s">
-        <v>85</v>
+      <c r="E28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B29">
+        <v>26</v>
+      </c>
+      <c r="C29">
+        <v>3003</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B30">
+        <v>27</v>
+      </c>
+      <c r="C30">
+        <v>3003</v>
+      </c>
+      <c r="D30">
+        <v>5</v>
+      </c>
+      <c r="E30" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B31">
+        <v>28</v>
+      </c>
+      <c r="C31">
+        <v>3003</v>
+      </c>
+      <c r="D31">
+        <v>6</v>
+      </c>
+      <c r="E31" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B32">
+        <v>29</v>
+      </c>
+      <c r="C32">
+        <v>3003</v>
+      </c>
+      <c r="D32">
+        <v>7</v>
+      </c>
+      <c r="E32" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B33">
+        <v>30</v>
+      </c>
+      <c r="C33">
+        <v>3003</v>
+      </c>
+      <c r="D33">
+        <v>8</v>
+      </c>
+      <c r="E33" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="108">
   <si>
     <t>!Enum</t>
   </si>
@@ -327,6 +327,29 @@
   </si>
   <si>
     <t>Skill_Monster_Boss_MeleeAttack_01</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>RespawnType</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>초 단위 리젠 (RespawnTime)</t>
+  </si>
+  <si>
+    <t>DailyReset</t>
+  </si>
+  <si>
+    <t>콘텐츠 초기화 시각(06시) 리젠</t>
+  </si>
+  <si>
+    <t>RespawnType</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!RespawnType</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -887,7 +910,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="1" bestFit="1" customWidth="1"/>
@@ -984,6 +1007,30 @@
       </c>
       <c r="C14" s="2" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -2518,7 +2565,9 @@
       <c r="H2" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="2"/>
+      <c r="I2" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
@@ -2543,7 +2592,9 @@
       <c r="H3" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="2"/>
+      <c r="I3" s="16" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="7"/>
@@ -2778,7 +2829,9 @@
         <v>10</v>
       </c>
       <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
+      <c r="I14" s="2" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>

--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="633" activeTab="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="633" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -902,7 +902,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1787,7 +1787,7 @@
         <v>63</v>
       </c>
       <c r="E8" s="2">
-        <v>850</v>
+        <v>350</v>
       </c>
       <c r="F8" s="2">
         <v>10</v>

--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -902,7 +902,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1393,7 +1393,9 @@
       <c r="M8">
         <v>500</v>
       </c>
-      <c r="O8" s="2"/>
+      <c r="O8" s="2">
+        <v>9101</v>
+      </c>
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
